--- a/assets/downloads/tables/taxonomy_2026-03-23.xlsx
+++ b/assets/downloads/tables/taxonomy_2026-03-23.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>synonym:HowardMoore</t>
+          <t>synonym:IOC-lump</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Turdus poliocephalus</t>
+          <t>Chamaetylas poliocephala</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Turdus poliocephalus</t>
+          <t>Chamaetylas poliocephala</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Turdidae (Thrushes and Allies)</t>
+          <t>Muscicapidae (Old World Flycatchers)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>synonym:IOC-lump</t>
         </is>
       </c>
     </row>
@@ -31770,12 +31770,12 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Crithagra frontalis</t>
+          <t>Sphenopsis frontalis</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Crithagra frontalis</t>
+          <t>Hemispingus frontalis</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
@@ -31785,12 +31785,12 @@
       </c>
       <c r="E985" t="inlineStr">
         <is>
-          <t>Fringillidae (Finches, Euphonias, and Allies)</t>
+          <t>Thraupidae (Tanagers and Allies)</t>
         </is>
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -33806,7 +33806,7 @@
       </c>
       <c r="F1048" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>synonym:BirdLife-lump</t>
         </is>
       </c>
     </row>
@@ -34842,12 +34842,12 @@
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Copsychus albiventris</t>
+          <t>Copsychus malabaricus</t>
         </is>
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Copsychus albiventris</t>
+          <t>Kittacincla malabarica</t>
         </is>
       </c>
       <c r="D1081" t="inlineStr">
@@ -34862,7 +34862,7 @@
       </c>
       <c r="F1081" t="inlineStr">
         <is>
-          <t>synonym:HowardMoore</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -37978,12 +37978,12 @@
       </c>
       <c r="B1179" t="inlineStr">
         <is>
-          <t>Euphonia violacea</t>
+          <t>Melopyrrha violacea</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Euphonia violacea</t>
+          <t>Loxigilla violacea</t>
         </is>
       </c>
       <c r="D1179" t="inlineStr">
@@ -37993,12 +37993,12 @@
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>Fringillidae (Finches, Euphonias, and Allies)</t>
+          <t>Thraupidae (Tanagers and Allies)</t>
         </is>
       </c>
       <c r="F1179" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -50718,12 +50718,12 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Metallura baroni</t>
+          <t>Phaethornis longirostris</t>
         </is>
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>Metallura baroni</t>
+          <t>Phaethornis longirostris longirostris</t>
         </is>
       </c>
       <c r="D1579" t="inlineStr">
@@ -50738,7 +50738,7 @@
       </c>
       <c r="F1579" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>synonym:BirdLife-lump</t>
         </is>
       </c>
     </row>
@@ -54258,7 +54258,7 @@
       </c>
       <c r="F1689" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -54290,7 +54290,7 @@
       </c>
       <c r="F1690" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -66510,7 +66510,7 @@
       </c>
       <c r="F2075" t="inlineStr">
         <is>
-          <t>synonym:HowardMoore</t>
+          <t>synonym:BirdLife-lump</t>
         </is>
       </c>
     </row>
@@ -66958,7 +66958,7 @@
       </c>
       <c r="F2089" t="inlineStr">
         <is>
-          <t>synonym:HowardMoore</t>
+          <t>synonym:BirdLife-lump</t>
         </is>
       </c>
     </row>
@@ -68474,12 +68474,12 @@
       </c>
       <c r="B2137" t="inlineStr">
         <is>
-          <t>Chlorophonia cyanocephala</t>
+          <t>Sporathraupis cyanocephala</t>
         </is>
       </c>
       <c r="C2137" t="inlineStr">
         <is>
-          <t>Euphonia cyanocephala</t>
+          <t>Thraupis cyanocephala</t>
         </is>
       </c>
       <c r="D2137" t="inlineStr">
@@ -68489,12 +68489,12 @@
       </c>
       <c r="E2137" t="inlineStr">
         <is>
-          <t>Fringillidae (Finches, Euphonias, and Allies)</t>
+          <t>Thraupidae (Tanagers and Allies)</t>
         </is>
       </c>
       <c r="F2137" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -68986,12 +68986,12 @@
       </c>
       <c r="B2153" t="inlineStr">
         <is>
-          <t>Akialoa obscura</t>
+          <t>Asemospiza obscura</t>
         </is>
       </c>
       <c r="C2153" t="inlineStr">
         <is>
-          <t>Akialoa obscura</t>
+          <t>Tiaris obscura</t>
         </is>
       </c>
       <c r="D2153" t="inlineStr">
@@ -69001,12 +69001,12 @@
       </c>
       <c r="E2153" t="inlineStr">
         <is>
-          <t>Fringillidae (Finches, Euphonias, and Allies)</t>
+          <t>Thraupidae (Tanagers and Allies)</t>
         </is>
       </c>
       <c r="F2153" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -70170,12 +70170,12 @@
       </c>
       <c r="B2190" t="inlineStr">
         <is>
-          <t>Mixornis gularis</t>
+          <t>Argya gularis</t>
         </is>
       </c>
       <c r="C2190" t="inlineStr">
         <is>
-          <t>Mixornis gularis</t>
+          <t>Argya gularis</t>
         </is>
       </c>
       <c r="D2190" t="inlineStr">
@@ -70185,12 +70185,12 @@
       </c>
       <c r="E2190" t="inlineStr">
         <is>
-          <t>Timaliidae (Tree-Babblers, Scimitar-Babblers, and Allies)</t>
+          <t>Leiothrichidae (Laughingthrushes and Allies)</t>
         </is>
       </c>
       <c r="F2190" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -72378,12 +72378,12 @@
       </c>
       <c r="B2259" t="inlineStr">
         <is>
-          <t>Setophaga pinus</t>
+          <t>Vermivora cyanoptera</t>
         </is>
       </c>
       <c r="C2259" t="inlineStr">
         <is>
-          <t>Setophaga pinus</t>
+          <t>Vermivora cyanoptera</t>
         </is>
       </c>
       <c r="D2259" t="inlineStr">
@@ -72398,7 +72398,7 @@
       </c>
       <c r="F2259" t="inlineStr">
         <is>
-          <t>reassigned:family</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
@@ -74246,12 +74246,12 @@
       </c>
       <c r="B2318" t="inlineStr">
         <is>
-          <t>Zosterops pallidus</t>
+          <t>Zosterops virens</t>
         </is>
       </c>
       <c r="C2318" t="inlineStr">
         <is>
-          <t>Zosterops pallidus</t>
+          <t>Zosterops virens</t>
         </is>
       </c>
       <c r="D2318" t="inlineStr">
@@ -74266,7 +74266,7 @@
       </c>
       <c r="F2318" t="inlineStr">
         <is>
-          <t>legacy</t>
+          <t>manual</t>
         </is>
       </c>
     </row>
